--- a/Data/EXCEL/Transfer/salemon/202412/2928-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/2928-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE71DEAC-94D6-43A7-91C8-7591F55806FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7860F33-5CB1-4F24-AD88-A7C60873BAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{E6E34A8B-3BF8-4983-85D6-2DC3C66A620D}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{BEB48923-61CA-4692-983A-6E8E4C87520D}"/>
   </bookViews>
   <sheets>
     <sheet name="2928-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1234,19 +1234,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB1C93CC-7C00-4BFE-B3C4-48C61DEBA674}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E4E177-9180-474C-ADD6-F4CBE22A33B9}">
   <dimension ref="A1:Q5"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="10" width="14.6328125" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" customWidth="1"/>
-    <col min="12" max="15" width="14.6328125" customWidth="1"/>
-    <col min="16" max="16" width="15.453125" customWidth="1"/>
-    <col min="17" max="17" width="15.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10.125" customWidth="1"/>
+    <col min="12" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="10.125" customWidth="1"/>
+    <col min="17" max="17" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="P1" s="14"/>
       <c r="Q1" s="15"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="10" t="s">
         <v>4</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1355,7 +1355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1394,7 +1394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44440</v>
       </c>
